--- a/DOCS/ThingEdu_GCompris-vi_DoiChieu_GDPT2018_NLS2025_CV3456.xlsx
+++ b/DOCS/ThingEdu_GCompris-vi_DoiChieu_GDPT2018_NLS2025_CV3456.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HuongDan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TongHop" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="GDPT2018-MonHoc" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GDPT2018-NangLuc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NLS-TT02-2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CV3456-TrienKhai" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Papert-Maker" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="HoatDong-202" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CanThietKeLai" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HuongDan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TongHop" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GDPT2018-MonHoc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GDPT2018-NangLuc" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NLS-TT02-2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CV3456-TrienKhai" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Papert-Maker" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoatDong-202" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CanThietKeLai" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'HoatDong-202'!$A$4:$I$206</definedName>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Mạch điện tương tự • Hộp thăng bằng • Bóng đèn nhị phân • Vận hành âu thuyền • Học xem đồng hồ • Pha màu sơn</t>
+          <t>Mạch điện tương tự • Hộp thăng bằng • Bóng đèn nhị phân • Cho thuyền qua âu tàu • Học xem đồng hồ • Pha màu sơn</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Trang soạn thảo đầu tiên của bé • Bấm và vẽ • La bàn • Vẽ bằng bánh răng • Sáng tác dương cầm • Vẽ lại hình mẫu</t>
+          <t>Trang soạn thảo đầu tiên của bé • Bấm và vẽ • Vẽ bằng compa • Vẽ bằng bánh răng • Sáng tác dương cầm • Vẽ lại hình mẫu</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Thước mét dán lên tường, trẻ dán kẹp giấy vào đúng vạch được đọc lên.</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Dải hoa văn bằng nắp chai, hạt và giấy màu dán trên băng giấy dài quanh lớp.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Bạn A đọc dãy lệnh, bạn B bịt mắt đi theo trong lớp.</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Bạn A đọc lệnh quay trái, quay phải; bạn B bịt mắt làm theo — hướng tính theo thân mình.</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Rổ cam, quýt thật để trẻ đếm và bốc đúng số lượng.</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Trẻ viết dãy lệnh ra thẻ giấy để bạn khác đi theo mà tới đúng chỗ.</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Trẻ viết lệnh quay trái, quay phải ra thẻ giấy cho bạn bịt mắt đi theo.</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Thước mét dán lên tường, trẻ chỉ và đọc vạch.</t>
         </is>
       </c>
     </row>
@@ -3844,12 +3844,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Cân cho thăng bằng</t>
+          <t>Cho thuyền qua âu tàu</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>scalesboard</t>
+          <t>canal_lock</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Cân đĩa thật với quả cân tự làm từ đồng xu, hạt.</t>
+          <t>Âu tàu bằng hai hộp nhựa nối ống: đổ nước, mở van, xem thuyền giấy lên xuống theo mực nước.</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Học xem đồng hồ</t>
+          <t>Cân cho thăng bằng</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>clockgame</t>
+          <t>scalesboard</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Đồng hồ giấy có kim xoay được, tự làm.</t>
+          <t>Cân đĩa thật với quả cân tự làm từ đồng xu, hạt.</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Hộp thăng bằng</t>
+          <t>Học xem đồng hồ</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>balancebox</t>
+          <t>clockgame</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Tin học</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>5.1 Giải quyết vấn đề kỹ thuật</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Mê cung nghiêng bằng bìa và bi ve.</t>
+          <t>Đồng hồ giấy có kim xoay được, tự làm.</t>
         </is>
       </c>
     </row>
@@ -3979,12 +3979,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Vận hành âu thuyền</t>
+          <t>Hộp thăng bằng</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>canal_lock</t>
+          <t>balancebox</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
+          <t>Tin học</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
+          <t>5.1 Giải quyết vấn đề kỹ thuật</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Mê cung nghiêng bằng bìa và bi ve.</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Tám cái đèn pin hoặc tám tấm bìa lật, mỗi cái một giá trị 1-2-4-8… Trẻ bật tắt để đếm.</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Thả quả bóng từ các độ cao khác nhau, bấm giờ và ghi lại — cảm nhận gia tốc trước.</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Mười que tính bó thành một bó — một bó là một đơn vị, một que là một phần mười.</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Chai nhựa có lỗ và ống hút làm tàu ngầm cartesian: bóp chai thì chìm, thả ra thì nổi.</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>La bàn</t>
+          <t>Vẽ bằng bánh răng</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>compass</t>
+          <t>drawing_wheels</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>Compa thật trên giấy.</t>
+          <t>Vẽ, cắt, dán trên giấy thật.</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Vẽ bằng bánh răng</t>
+          <t>Vẽ bằng compa</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>drawing_wheels</t>
+          <t>compass</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>Vẽ, cắt, dán trên giấy thật.</t>
+          <t>Compa thật trên giấy.</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Trò trượt ô xếp hình</t>
+          <t>Trò trượt xe trong bãi đỗ</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Chạm đúp hoặc bấm đúp</t>
+          <t>Bắt số theo thứ tự</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>erase_2clic</t>
+          <t>planegame</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>Tin học</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>5.1 Giải quyết vấn đề kỹ thuật</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
         </is>
       </c>
       <c r="H113" s="8" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>Bàn phím cũ tháo rời cho trẻ sờ và gọi tên phím.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -8299,12 +8299,12 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Chỉ đúng người thân</t>
+          <t>Chạm đúp hoặc bấm đúp</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>family_find_relative</t>
+          <t>erase_2clic</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>Lịch sử và Địa lí</t>
+          <t>Tin học</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
+          <t>5.1 Giải quyết vấn đề kỹ thuật</t>
         </is>
       </c>
       <c r="H114" s="10" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="I114" s="10" t="inlineStr">
         <is>
-          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
+          <t>Bàn phím cũ tháo rời cho trẻ sờ và gọi tên phím.</t>
         </is>
       </c>
     </row>
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Chữ cái nằm trong từ nào</t>
+          <t>Chỉ đúng người thân</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>letter-in-word</t>
+          <t>family_find_relative</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>Tiếng Việt</t>
+          <t>Lịch sử và Địa lí</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
+          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
         </is>
       </c>
     </row>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Chữ cái rơi</t>
+          <t>Chữ cái nằm trong từ nào</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>gletters</t>
+          <t>letter-in-word</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>5.1 Giải quyết vấn đề kỹ thuật</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
         </is>
       </c>
       <c r="H116" s="10" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="I116" s="10" t="inlineStr">
         <is>
-          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
+          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Gia đình</t>
+          <t>Chữ cái rơi</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>gletters</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>Lịch sử và Địa lí</t>
+          <t>Tiếng Việt</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
+          <t>5.1 Giải quyết vấn đề kỹ thuật</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
+          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -8479,12 +8479,12 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Giai điệu</t>
+          <t>Gia đình</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>melody</t>
+          <t>family</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>Âm nhạc</t>
+          <t>Lịch sử và Địa lí</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I118" s="10" t="inlineStr">
         <is>
-          <t>Bộ chai nước gõ theo cao độ.</t>
+          <t>Dòng thời gian bằng dây và kẹp ảnh treo ngang lớp.</t>
         </is>
       </c>
     </row>
@@ -8524,12 +8524,12 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Học phép cộng</t>
+          <t>Giai điệu</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>learn_additions</t>
+          <t>melody</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Âm nhạc</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
+          <t>Bộ chai nước gõ theo cao độ.</t>
         </is>
       </c>
     </row>
@@ -8569,12 +8569,12 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Học phép trừ</t>
+          <t>Học phép cộng</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>learn_subtractions</t>
+          <t>learn_additions</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Khám phá vật nuôi trong trang trại</t>
+          <t>Học phép trừ</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>explore_farm_animals</t>
+          <t>learn_subtractions</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
+          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
         </is>
       </c>
     </row>
@@ -8659,12 +8659,12 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Luyện cộng bằng trò bắn bia</t>
+          <t>Khám phá vật nuôi trong trang trại</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>target</t>
+          <t>explore_farm_animals</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Tự nhiên và Xã hội (TH) · Khoa học · KHTN</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
         </is>
       </c>
       <c r="H122" s="10" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I122" s="10" t="inlineStr">
         <is>
-          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
+          <t>Làm lại thí nghiệm bằng vật liệu thật trong Làng.</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Mũ ảo thuật (phép cộng)</t>
+          <t>Luyện cộng bằng trò bắn bia</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>magic-hat-plus</t>
+          <t>target</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Mũ ảo thuật (phép trừ)</t>
+          <t>Mũ ảo thuật (phép cộng)</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>magic-hat-minus</t>
+          <t>magic-hat-plus</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Nối số theo thứ tự</t>
+          <t>Mũ ảo thuật (phép trừ)</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>number_sequence</t>
+          <t>magic-hat-minus</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Que tính, hạt, nắp chai — làm phép tính bằng tay trước.</t>
         </is>
       </c>
     </row>
@@ -8839,12 +8839,12 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Phân biệt tay trái, tay phải</t>
+          <t>Nối số theo thứ tự</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>leftright</t>
+          <t>number_sequence</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>Hoạt động trải nghiệm</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="I126" s="10" t="inlineStr">
         <is>
-          <t>Bộ xếp hình cắt từ bìa.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>So sánh số</t>
+          <t>Phân biệt tay trái, tay phải</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>comparator</t>
+          <t>leftright</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Hoạt động trải nghiệm</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Bộ xếp hình cắt từ bìa.</t>
         </is>
       </c>
     </row>
@@ -8929,12 +8929,12 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Sắp chữ cái theo thứ tự</t>
+          <t>So sánh số</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>ordering_alphabets</t>
+          <t>comparator</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="G128" s="10" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="I128" s="10" t="inlineStr">
         <is>
-          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -8974,12 +8974,12 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Sắp câu cho đúng</t>
+          <t>Sắp chữ cái theo thứ tự</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>ordering_sentences</t>
+          <t>ordering_alphabets</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
+          <t>Thẻ chữ cắt rời, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -9019,12 +9019,12 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Sắp số theo thứ tự</t>
+          <t>Sắp câu cho đúng</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>ordering_numbers</t>
+          <t>ordering_sentences</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Tiếng Việt</t>
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="I130" s="10" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Thẻ chữ và tranh, ghép trên bàn.</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Sắp sự kiện theo thời gian</t>
+          <t>Sắp số theo thứ tự</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>ordering_chronology</t>
+          <t>ordering_numbers</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>Hoạt động trải nghiệm</t>
+          <t>Toán</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
+          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
         </is>
       </c>
       <c r="H131" s="8" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>Vật thật xếp theo quy luật trên bàn.</t>
+          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Sắp theo thứ tự số</t>
+          <t>Sắp sự kiện theo thời gian</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>planegame</t>
+          <t>ordering_chronology</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>Toán</t>
+          <t>Hoạt động trải nghiệm</t>
         </is>
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>5.3 Sử dụng sáng tạo công nghệ số</t>
+          <t>1.1 Duyệt, tìm kiếm và lọc dữ liệu</t>
         </is>
       </c>
       <c r="H132" s="10" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="I132" s="10" t="inlineStr">
         <is>
-          <t>Đếm và đo bằng vật thật trước khi lên màn hình.</t>
+          <t>Vật thật xếp theo quy luật trên bàn.</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Phép trừ đặt tính dọc (có nhớ)</t>
+          <t>Phép trừ đặt tính dọc (kiểu bù trừ)</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">

--- a/DOCS/ThingEdu_GCompris-vi_DoiChieu_GDPT2018_NLS2025_CV3456.xlsx
+++ b/DOCS/ThingEdu_GCompris-vi_DoiChieu_GDPT2018_NLS2025_CV3456.xlsx
@@ -12494,7 +12494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12602,79 +12602,133 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Bản đồ Việt Nam</t>
+          <t>CHỦ QUYỀN — bản đồ Việt Nam thiếu Hoàng Sa và Trường Sa</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Tìm quốc gia trên bản đồ · Tìm vùng trên bản đồ</t>
+          <t>Tìm quốc gia trên bản đồ (cấp 12 Đông Nam Á)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bộ bản đồ hiện có gồm châu Âu, Mỹ, Ấn Độ, Trung Quốc, Úc, Scotland, Romania, Litva… KHÔNG có bản đồ Việt Nam.</t>
+          <t>Tệp vietnam.svgz chỉ vẽ phần đất liền và vài đảo ven bờ. KHÔNG có quần đảo Hoàng Sa, KHÔNG có quần đảo Trường Sa. Nền bản đồ Đông Nam Á cũng để Biển Đông hoàn toàn trống. Điểm tích cực: bản đồ Trung Quốc không có đường lưỡi bò.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Không dùng được cho phần Địa lí Việt Nam của môn Lịch sử và Địa lí.</t>
+          <t>VI PHẠM Nghị định 18/2020/NĐ-CP Điều 11 khoản 2: lưu hành sản phẩm bản đồ liên quan chủ quyền mà không thể hiện đúng chủ quyền bị phạt 30-40 triệu đồng, tịch thu tang vật và buộc cải chính. Tuyệt đối không đưa vào lớp học ở dạng hiện tại.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Bổ sung bộ bản đồ 34 tỉnh thành. GCompris cho thêm bộ bản đồ mới mà không phải sửa mã nguồn.</t>
+          <t>1) Khoá ngay hai hoạt động bản đồ khỏi bản dùng trong trường. 2) Vẽ lại vietnam.svgz và nền southeast_asia.svgz có đủ hai quần đảo, kèm nhãn. 3) Gửi bản vá lên KDE. Xem DOCS/LUU_Y_BAN_DO_CHU_QUYEN.md.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Bộ từ theo cấp độ âm tiết</t>
+          <t>Bản đồ hành chính Việt Nam</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Chữ cái rơi · Từ rơi · Trò đoán chữ · Bấm vào chữ cái</t>
+          <t>Tìm vùng trên bản đồ</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Các hoạt động này xây trên giả định 'chữ cái rời ghép thành từ'. Tiếng Việt có 29 chữ cái, thêm ă â đ ê ô ơ ư, 5 dấu thanh nằm trên nguyên âm, và đơn vị đọc là âm tiết.</t>
+          <t>18 bộ bản đồ hành chính: Ý, Ấn Độ, Trung Quốc, Úc, Mỹ, Pháp, Đức, Scotland, Romania, Litva… KHÔNG có Việt Nam.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Trẻ gõ chữ cái rời theo lối tiếng Anh, không khớp cách học vần lớp 1.</t>
+          <t>Không dùng được cho phần Địa lí Việt Nam của môn Lịch sử và Địa lí.</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Soạn bộ từ default-vi.json theo cấp độ âm tiết cho Chữ cái rơi và Từ rơi. Bảng chữ cái tiếng Việt đã việt hóa xong cho Thứ tự bảng chữ cái và Sắp chữ cái theo thứ tự.</t>
+          <t>Bổ sung bộ bản đồ 34 tỉnh thành. GCompris cho thêm bộ bản đồ mới mà không phải sửa mã nguồn.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
+          <t>Đài Loan liệt ngang hàng quốc gia</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Tìm quốc gia trên bản đồ (cấp 13 Đông Á)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Cấp Đông Á xếp Đài Loan thành một mảnh riêng, ngang với Trung Quốc, Nhật Bản, Hàn Quốc.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Việt Nam theo chính sách Một Trung Quốc; sách giáo khoa Việt Nam không liệt Đài Loan là quốc gia.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Nhà trường cân nhắc: bỏ cấp Đông Á, hoặc giữ và giải thích. Cần chủ dự án chốt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Bộ từ theo cấp độ âm tiết</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Chữ cái rơi · Từ rơi · Trò đoán chữ · Bấm vào chữ cái</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Các hoạt động này xây trên giả định 'chữ cái rời ghép thành từ'. Tiếng Việt có 29 chữ cái, thêm ă â đ ê ô ơ ư, 5 dấu thanh nằm trên nguyên âm, và đơn vị đọc là âm tiết.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Trẻ gõ chữ cái rời theo lối tiếng Anh, không khớp cách học vần lớp 1.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Soạn bộ từ default-vi.json theo cấp độ âm tiết cho Chữ cái rơi và Từ rơi. Bảng chữ cái tiếng Việt đã việt hóa xong cho Thứ tự bảng chữ cái và Sắp chữ cái theo thứ tự.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>(bổ sung) Kho giọng đọc chưa đủ</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Mở rộng vốn từ · các hoạt động địa lí</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Mới sinh 202/888 tệp giọng. Còn thiếu 564 từ vựng và 129 tên nước.</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Hoạt động Mở rộng vốn từ chưa dùng được; trẻ chưa biết đọc sẽ mất phần nghe.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Sinh nốt bằng VieNeu-TTS sau khi dịch content-vi.json (1.090 từ).</t>
         </is>
